--- a/Config/Datas/alchemy.xlsx
+++ b/Config/Datas/alchemy.xlsx
@@ -13,7 +13,6 @@
     <sheet name="alchemy_furnace" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="alchemy_tool" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="alchemy_recipe" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="alchemy_progress" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1440,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1493,11 @@
           <t>required_tools</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>owner_item_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1546,6 +1550,11 @@
           <t>(list#sep=|),string</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1598,6 +1607,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1630,6 +1644,11 @@
           <t>必须持有的工具 item_id</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>对应道具 item_id，空=不可作为持有物</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -1659,6 +1678,11 @@
       <c r="I5" t="n">
         <v>25</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>furn_basic_cauldron</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -1698,6 +1722,11 @@
           <t>tool_mortar</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>furn_stone_retort</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -1736,6 +1765,35 @@
         <is>
           <t>tool_mortar|tool_glass_rod|tool_alchemy_kit</t>
         </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>furn_arcane_crucible</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>furn_hand_craft</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>手搓</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2703,240 +2761,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>extra_material_slots</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>unlock_mode</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>unlock_param</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>unlock_item_min_count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EForgeUnlockMode</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>在炉子基础上追加的素材格</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>入门</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>熟练</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HasItem</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mat_alchemical_glass|1</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>精通</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HasItem</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>mat_alchemical_gel|3</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>大师</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HasItem</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mat_runed_stone|1</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>